--- a/exports/colleges/17904_isb-hyderabad-indian-school-of-business-hyderabad.xlsx
+++ b/exports/colleges/17904_isb-hyderabad-indian-school-of-business-hyderabad.xlsx
@@ -605,19 +605,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
     <col width="61" customWidth="1" min="3" max="3"/>
     <col width="61" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
@@ -707,12 +707,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>45.12 Lakhs</t>
+          <t>45.12 L</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Graduation + GMAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>GMAT, GRE</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>8 Oct - 25 Jan 2026</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -769,12 +769,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>37.38 Lakhs</t>
+          <t>37.38 L</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1 Year 6 Months</t>
+          <t>1 year 6 months</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -784,17 +784,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Graduation</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>GMAT</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Oct - 19 Apr 2026</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5 Years</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -846,17 +846,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Post Graduation + GMAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>15 Oct - 30 Jan 2026</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PG Diploma in Management</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>49.91 Lakhs</t>
+          <t>49.91 L</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1 Year 3 Months</t>
+          <t>1 year 3 months</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Graduation + BAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>GMAT, GRE</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Nov - 30 Mar 2026</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Graduate Certificate in Management</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -955,12 +955,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>36.15 Lakhs</t>
+          <t>36.15 L</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1 Year 8 Months</t>
+          <t>1 year 8 months</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -970,17 +970,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Graduation + GMAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>15 Feb - 31 May 2026</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1002,32 +1002,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>Executive Programme</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>Executive Fellow Programme in Management</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>Executive Fellow Programme in Management</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10.71 Lakhs - 33.6 Lakhs</t>
+          <t>47.6 L</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>15 Oct - 30 Jan 2026</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>Advanced Management Program in Business Analytics</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>Advanced Management Program in Business Analytics</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10.71 Lakhs - 33.6 Lakhs</t>
+          <t>11.05 L</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 year 3 months</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Total Fees (2026 - 2027)</t>
+          <t>Advanced Management Program</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Total Fees (2026 - 2027)</t>
+          <t>Advanced Management Program</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Total Fees (2026 - 2027)</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11.05 Lakhs</t>
+          <t>10.71 L - 14.06 L</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1188,37 +1188,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Advanced Diploma in Operations Management</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Advanced Diploma in Operations Management</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>13.4 Lakhs</t>
+          <t>11.44 L</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Graduation</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1250,27 +1250,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Operations &amp; Supply Chain</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Operations &amp; Supply Chain</t>
+          <t>Post Graduate Programme in Management [PGPM]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Operations &amp; Supply Chain</t>
+          <t>Post Graduate Programme in Management [PGPM]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11.44 Lakhs</t>
+          <t>45.12 Lakhs</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Year</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Graduation</t>
+          <t>Graduation + GMAT</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GMAT, GRE</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1312,32 +1312,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Post Graduate Programme in Management (Working Executives)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Post Graduate Programme in Management (Working Executives)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>10.71 Lakhs</t>
+          <t>37.38 Lakhs</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Year 6 Months</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GMAT</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1374,27 +1374,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Public Policy</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Public Policy</t>
+          <t>Fellow Programme in Management [FPM]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Public Policy</t>
+          <t>Fellow Programme in Management [FPM]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>14.01 Lakhs</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>5 Years</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Graduation</t>
+          <t>Post Graduation + GMAT</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1436,27 +1436,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>PG Diploma in Management</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>Post Graduate Program in Family Managed Business [PGPFMB]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>Post Graduate Program in Family Managed Business [PGPFMB]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>37.38 Lakhs - 49.5 Lakhs</t>
+          <t>49.91 Lakhs</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Year 3 Months</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation + BAT</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GMAT, GRE</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1498,27 +1498,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>Graduate Certificate in Management</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>Post Graduate Programme in Management for Young Leaders</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>Post Graduate Programme in Management for Young Leaders</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>37.38 Lakhs - 49.5 Lakhs</t>
+          <t>36.15 Lakhs</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Year 8 Months</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation + GMAT</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1560,22 +1560,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>49.91 Lakhs</t>
+          <t>13.4 Lakhs</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1622,22 +1622,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>Operations &amp; Supply Chain</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>Operations &amp; Supply Chain</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>Operations &amp; Supply Chain</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>49.91 Lakhs</t>
+          <t>11.44 Lakhs</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1684,33 +1684,37 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PGPX</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PGPX (General)</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>10.71 Lakhs</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>Graduation</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1742,51 +1746,171 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>Public Policy</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Public Policy</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Public Policy</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>14.01 Lakhs</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Graduation</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>17904</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PGPX</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PGPX (General)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Graduation</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>17904</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>EFPM</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>EFPM (General)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Post Graduation + GMAT</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
         <is>
           <t>Full Time</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>UG</t>
         </is>
